--- a/public/sample-questions-import.xlsx
+++ b/public/sample-questions-import.xlsx
@@ -434,16 +434,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Linh Hồn Của Cỗ Máy</v>
+        <v>Khởi Nguyên</v>
       </c>
       <c r="B2" t="str">
-        <v>Mai là một BA Fresher vừa gia nhập công ty phần mềm X. Ngày đầu tiên đi làm, cô chứng kiến đội Dev sử dụng một công cụ AI để tự động sinh ra mã nguồn từ vài dòng mô tả ngắn gọn. Thậm chí, một số tài liệu quy trình cũng được AI tự động vẽ ra nhanh chóng. Mai cảm thấy hoang mang và tự hỏi: "Nếu AI có thể tự động hóa việc viết code và vẽ quy trình, vậy giá trị cốt lõi của một BA thực thụ nằm ở đâu để không bị thay thế?". Bạn hãy giúp Mai xác định đâu là câu trả lời đúng nhất mang tính bản chất của nghề BA.</v>
+        <v>Mai vừa tiếp nhận dự án làm lại hệ thống ERP cho một tập đoàn sản xuất đồ gỗ. Khối lượng tài liệu quy trình cũ (SOP) lên đến hàng ngàn trang PDF. Theo phương pháp luận truyền thống, Mai sẽ mất hàng tuần chỉ để đọc hiểu. Nhớ lại triết lý "AI-First", cô quyết định dùng AI để thiết lập hệ thống tri thức. Tuy nhiên, hành động đầu tiên cô làm không phải là quăng tất cả tài liệu vào AI một cách mù quáng, mà là một bước tư duy nền tảng. Theo bạn, hành động đầu tiên và quan trọng nhất của Mai để làm chủ khối dữ liệu này là gì?</v>
       </c>
       <c r="C2" t="str">
         <v>single</v>
       </c>
       <c r="D2" t="str">
-        <v>["Khả năng tạo ra các tài liệu SRS/User Story bóng bẩy, chuẩn chỉnh","Khả năng thấu cảm, tư duy phản biện và giao tiếp giải quyết xung đột với khách hàng","Khả năng viết code nhanh hơn AI","Khả năng thiết kế giao diện UI/UX đẹp mắt"]</v>
+        <v>["Cắt nhỏ file PDF thành nhiều phần và yêu cầu AI tóm tắt từng phần","Lên danh sách các mục tiêu nghiệp vụ cốt lõi cần giải quyết trước khi cung cấp bối cảnh (context) cho AI","Dùng Python viết một script OCR để chuyển đổi PDF sang text thuần túy","Hỏi AI cách để tự động hóa toàn bộ nhà máy sản xuất gỗ"]</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -452,190 +452,190 @@
         <v/>
       </c>
       <c r="G2" t="str">
-        <v>Giá trị cốt lõi của BA là trí tuệ cảm xúc, khả năng thấu cảm và tư duy phản biện - những thứ AI chưa thể thay thế.</v>
+        <v>Sự khác biệt của một AI-Driven BA là bắt đầu từ tư duy giải quyết vấn đề (Problem-Solving) và mục tiêu nghiệp vụ, chứ không phải bị lệ thuộc vào công cụ. Cần xác định mục tiêu trước khi Prompt.</v>
       </c>
       <c r="H2" t="str">
-        <v>Bản chất BA,Fresher</v>
+        <v>Tư duy AI,Problem Solving</v>
       </c>
       <c r="I2">
         <v>1</v>
       </c>
       <c r="J2" t="str">
-        <v>Vai trò cốt lõi</v>
+        <v>Chiến lược phân tích</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Lời Thì Thầm Của Dữ Liệu</v>
+        <v>Nghịch Lý Lựa Chọn</v>
       </c>
       <c r="B3" t="str">
-        <v>Trong một dự án xây dựng hệ thống CRM, Mai muốn dùng ChatGPT để khởi tạo khung tài liệu User Story. Nhận ra Prompt ngây ngô sẽ cho ra kết quả vô dụng, Mai quyết định xây dựng một quy trình Prompting chuyên nghiệp từng bước một. Hãy giúp Mai sắp xếp trình tự hợp lý nhất để có một câu lệnh Prompt chất lượng cao.</v>
+        <v>Dự án đang trong giai đoạn đề xuất kiến trúc hệ thống. Mai dùng một LLM để phân tích và so sánh 3 giải pháp kiến trúc: Microservices, Monolithic và Serverless. AI đưa ra một bảng so sánh vô cùng thuyết phục, phân tích hàng loạt ưu điểm vượt trội và kết luận nên chọn Serverless vì khả năng mở rộng vô hạn. Tuy nhiên, với vai trò là BA, Mai biết rằng đội ngũ Dev hiện tại của công ty chỉ có kinh nghiệm bảo trì Monolithic, và ngân sách hạ tầng cho dự án này cực kỳ eo hẹp. Mai cần áp dụng những "Bộ lọc chống ảo tưởng" nào trước khi chốt phương án tư vấn cho khách hàng?</v>
       </c>
       <c r="C3" t="str">
-        <v>ordering</v>
+        <v>multiple</v>
       </c>
       <c r="D3" t="str">
-        <v>["Xác định rõ vai trò của AI (Ví dụ: \"Đóng vai một Senior BA chuyên về CRM...\")","Cung cấp bối cảnh (Context) và mục tiêu nghiệp vụ cụ thể của dự án","Cung cấp các dữ liệu đầu vào hoặc ví dụ mẫu (Examples)","Đưa ra yêu cầu cụ thể về định dạng đầu ra (Output Format)","Yêu cầu AI tự kiểm tra và phản biện lại kết quả vừa tạo (Self-Critique)"]</v>
+        <v>["Bộ lọc Công nghệ (Đánh giá giới hạn của bản thân LLM đang sử dụng)","Bộ lọc Nghiệp vụ (Đánh giá tính khả thi dựa trên năng lực hiện tại của tổ chức)","Bộ lọc Giá trị thực (Cân đối giữa ROI và chi phí bảo trì thực tế)","Bộ lọc Đạo đức (Đảm bảo kiến trúc không vi phạm quyền riêng tư)"]</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>[]</v>
+        <v>[1,2]</v>
       </c>
       <c r="G3" t="str">
-        <v>Một Prompt tốt cần đi từ thiết lập vai trò, bối cảnh, cung cấp dữ liệu, chỉ định đầu ra và cuối cùng là vòng lặp phản biện.</v>
+        <v>AI thường gợi ý giải pháp tốt nhất về mặt lý thuyết (sách giáo khoa). BA phải dùng Bộ lọc Nghiệp vụ (nhân lực thực tế) và Bộ lọc Giá trị thực (chi phí) để bẻ lái giải pháp cho phù hợp.</v>
       </c>
       <c r="H3" t="str">
-        <v>Prompting,Kỹ năng</v>
+        <v>Thẩm định,Kiến trúc</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3" t="str">
-        <v>Kỹ năng làm việc với AI</v>
+        <v>Thẩm định giải pháp</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Bộ Lọc Chống Ảo Tưởng</v>
+        <v>Dòng Chảy Hỗn Loạn</v>
       </c>
       <c r="B4" t="str">
-        <v>Trở thành một "AI Powered BA", Mai sử dụng AI để brainstorm các Edge Cases (Trường hợp ngoại lệ) cho chức năng thanh toán trực tuyến. AI liệt kê ra 20 trường hợp, trong đó có những trường hợp rất hiếm gặp và đòi hỏi chi phí phát triển cực lớn. Nhớ lại nguyên tắc làm việc mới, Mai hiểu rằng mình không thể trở thành "người chuyển phát tài liệu" của AI. Cô cần đóng vai trò là chuyên gia thẩm định thông qua các bộ lọc. Những bộ lọc tối cao nào Mai cần áp dụng trước khi đưa các Edge Cases này vào backlog? (Chọn nhiều đáp án)</v>
+        <v>Trong một dự án siêu tốc, khách hàng liên tục thay đổi yêu cầu kinh doanh, khiến tài liệu đặc tả (SRS) của Mai bị lỗi thời (out-of-date) ngay khi vừa viết xong. Mai quyết định dẹp bỏ phương pháp Thác nước (Waterfall) và chuyển sang luồng làm việc "Hyper-Agile" được trợ lực bởi AI (như Antigravity hoặc Cursor). Hãy giúp Mai sắp xếp vòng đời quản lý Yêu cầu siêu tốc theo tư duy hiện đại nhất.</v>
       </c>
       <c r="C4" t="str">
-        <v>multiple</v>
+        <v>ordering</v>
       </c>
       <c r="D4" t="str">
-        <v>["Bộ lọc Nghiệp vụ (Tính khả thi và giá trị thực tế)","Bộ lọc Ngôn ngữ (Đảm bảo văn phong chuyên nghiệp)","Bộ lọc Pháp lý &amp; Bảo mật (Đảm bảo tuân thủ tiêu chuẩn an toàn)","Bộ lọc Giá trị thực (Giải quyết đúng nỗi đau gốc rễ của khách hàng)"]</v>
+        <v>["Thu thập các ý tưởng rời rạc và yêu cầu thô từ khách hàng (Voice records, sticky notes)","Đưa yêu cầu thô vào AI Agent kèm theo bối cảnh dự án để sinh nhánh User Stories nền tảng","Dùng AI để sinh nhanh các bản phác thảo giao diện (Wireframes/Prototypes) từ User Stories","Cầm Prototype tương tác trực quan với khách hàng để chốt phương án và điều chỉnh ngay lập tức","AI tự động cập nhật lại các tài liệu đặc tả và test cases dựa trên Prototype cuối cùng"]</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>[0,2,3]</v>
+        <v>[]</v>
       </c>
       <c r="G4" t="str">
-        <v>BA cần đóng vai trò là chuyên gia thẩm định thông qua 3 bộ lọc: Nghiệp vụ, Pháp lý &amp; Bảo mật, và Giá trị thực.</v>
+        <v>Đây là quy trình định hướng (Directing) thay vì thu thập (Elicitation) tuyến tính. Đi từ ý tưởng thô -&gt; AI tạo Story -&gt; AI tạo Prototype -&gt; Tương tác trực quan chốt đơn -&gt; AI cập nhật tài liệu.</v>
       </c>
       <c r="H4" t="str">
-        <v>Thẩm định,Bộ lọc</v>
+        <v>Agile,Quy trình</v>
       </c>
       <c r="I4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J4" t="str">
-        <v>Thẩm định giải pháp</v>
+        <v>Chiến lược phân tích</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Nghệ Thuật Đàm Phán</v>
+        <v>Bức Tranh Mảnh Ghép</v>
       </c>
       <c r="B5" t="str">
-        <v>Cuộc họp giữa bộ phận Kinh doanh (của khách hàng) và Đội Kỹ thuật (của công ty Mai) diễn ra vô cùng căng thẳng. Khách hàng yêu cầu một tính năng "phải có ngay" nhưng kỹ thuật khẳng định "không thể làm kịp trong 2 tuần". Bầu không khí ngột ngạt và đầy thất vọng. Mai đang ở giữa cuộc chiến này. Cô có thể mang theo laptop có cài mô hình AI tiên tiến nhất. Liệu AI có thể thay thế Mai giải quyết được tình huống này không, và tại sao?</v>
+        <v>Công việc BA đòi hỏi sự đa nhiệm. Mai đang phải xử lý 4 tác vụ khó nhằn trong dự án ERP: (A) Tự động hóa việc phân tích luồng code cũ để tìm Business Rules; (B) Thiết kế giao diện Dashboard phân tích dữ liệu; (C) Chuyển biên bản họp thành danh sách công việc; (D) Xây dựng kế hoạch triển khai dài hạn. Mai có trong tay một bộ công cụ gồm các "vũ khí AI". Hãy ghép nối công cụ AI/Tính năng phù hợp nhất để Mai đạt hiệu suất tối đa.</v>
       </c>
       <c r="C5" t="str">
-        <v>single</v>
+        <v>matching</v>
       </c>
       <c r="D5" t="str">
-        <v>["Có. AI sẽ tính toán thời gian và phân chia task tối ưu nhất để ép cả hai bên đồng ý","Không. AI có thể phân tích dữ liệu nhưng không thể cảm nhận được sự thất vọng, thấu cảm và xây dựng lòng tin để gỡ rối xung đột giữa người với người","Có. AI sẽ gửi một bức email xin lỗi khách hàng cực kỳ mượt mà","Không. Vì AI chưa được cấp quyền truy cập vào Jira hay Confluence của dự án"]</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
+        <v>["Tìm ẩn số Business Rules từ mã nguồn dự án cũ (Legacy Code)","Tạo phác thảo giao diện (Wireframe) từ đoạn mô tả văn bản","Xử lý hội thoại tự nhiên từ biên bản họp thành danh sách Task","Hoạch định chiến lược và kế hoạch triển khai (Roadmap)"]</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
       </c>
       <c r="F5" t="str">
-        <v/>
+        <v>["Cursor / Claude Code (AI tích hợp IDE)","V0 / Midjourney / Figma AI (AI Design)","ChatGPT / Claude (LLM xử lý ngôn ngữ tự nhiên)","Antigravity / Trợ lý AI lập kế hoạch"]</v>
       </c>
       <c r="G5" t="str">
-        <v>AI không có Trí tuệ cảm xúc (Emotional Intelligence) và Sự thấu cảm (Empathy) để quản lý mâu thuẫn chính trị trong tổ chức.</v>
+        <v>Sử dụng đúng công cụ cho đúng bài toán là kỹ năng AI Tools Proficiency cốt lõi của một AI-Driven BA.</v>
       </c>
       <c r="H5" t="str">
-        <v>EQ,Đàm phán</v>
+        <v>AI Tools,Ứng dụng</v>
       </c>
       <c r="I5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J5" t="str">
-        <v>Trí tuệ cảm xúc</v>
+        <v>Kỹ năng làm việc với AI</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Ngã Ba Đường</v>
+        <v>Lời Thì Thầm Của Máy</v>
       </c>
       <c r="B6" t="str">
-        <v>Để không bị đào thải trong kỷ nguyên AI, Mai nhận ra mình cần bổ sung "vũ khí" mới. Cô quyết định phân loại rõ ràng đâu là Kỹ năng Kỹ thuật (Hard Skills) cần học, đâu là Kỹ năng Mềm (Soft Skills) vô giá. Hãy giúp Mai nối đúng nhóm cho mỗi kỹ năng.</v>
+        <v>Mai đang sử dụng tính năng Agentic AI của Antigravity để phân tích một quy trình đối soát tài chính phức tạp. Mai viết Prompt: "Hãy phân tích quy trình này và đưa ra các ngoại lệ (Edge cases)". AI trả về một danh sách các ngoại lệ rất ngô nghê, thiếu tính đặc thù ngành tài chính. Nhận ra "Điểm mù khẩu lệnh", Mai quyết định nâng cấp câu lệnh của mình bằng kỹ thuật Role-Prompting và Context-Seeding. Đâu là câu lệnh (Prompt) thể hiện đúng triết lý của một chuyên gia BA thực chiến?</v>
       </c>
       <c r="C6" t="str">
-        <v>matching</v>
+        <v>single</v>
       </c>
       <c r="D6" t="str">
-        <v>["Tư duy phản biện để thẩm định đầu ra của AI","Sử dụng PowerBI để trực quan hóa dữ liệu (Data Literacy)","Sự thấu cảm và đàm phán giải quyết xung đột (Empathy)","Thành thạo các công cụ tạo sinh (AI Tools Proficiency)"]</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
+        <v>["\"Bạn là một BA. Hãy nghĩ ra thêm nhiều trường hợp lỗi cho luồng tài chính này nhé.\"","\"Đóng vai trò là một Senior BA chuyên ngành Tài chính kế toán. Dựa vào bộ quy tắc chuẩn mực kế toán VAS kèm theo [tài liệu hệ thống hiện tại], hãy chỉ ra 5 lỗ hổng thất thoát dòng tiền có thể xảy ra ở bước chuyển khoản đối soát, và đề xuất hướng xử lý kỹ thuật.\"","\"Hãy mô tả lại quy trình đối soát tài chính dưới dạng bảng biểu để tôi dễ đọc hơn.\"","\"Viết cho tôi một câu lệnh SQL để truy vấn tất cả các giao dịch đối soát bị lỗi trong hệ thống.\""]</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
       </c>
       <c r="F6" t="str">
-        <v>["Soft Skills","Hard Skills","Soft Skills","Hard Skills"]</v>
+        <v/>
       </c>
       <c r="G6" t="str">
-        <v>Tư duy phản biện và thấu cảm là Soft Skills không thể thay thế. Data Literacy và AI Tools là Hard Skills mới của kỷ nguyên AI.</v>
+        <v>Prompt thực chiến phải có Role (Senior BA Tài chính), Context (Chuẩn mực VAS, tài liệu hiện tại), và Task rõ ràng (tìm 5 lỗ hổng thất thoát dòng tiền, đề xuất xử lý).</v>
       </c>
       <c r="H6" t="str">
-        <v>Kỹ năng mới,Hard Skills</v>
+        <v>Prompting,Thực chiến</v>
       </c>
       <c r="I6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J6" t="str">
-        <v>Nâng cấp kỹ năng</v>
+        <v>Kỹ năng làm việc với AI</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Cái Bẫy Của Kinh Nghiệm</v>
+        <v>Đứt Gãy Kết Nối</v>
       </c>
       <c r="B7" t="str">
-        <v>Sếp trực tiếp của Mai là anh Tuấn, một Senior BA với hơn 10 năm kinh nghiệm. Anh Tuấn luôn tự hào về bộ template tài liệu chuẩn mực mà anh mất nhiều năm xây dựng. Khi Mai đề xuất dùng AI để tự động hóa một số khâu viết tài liệu, anh Tuấn gạt phắt: "AI chỉ để giải trí, ảo tưởng lắm, không làm dự án thật được đâu. Đừng lười biếng mà phá hỏng quy trình". Là một người am hiểu làn sóng AI, bạn đánh giá rào cản cốt lõi nhất mà anh Tuấn đang vướng phải là gì?</v>
+        <v>Trong cuộc họp với Giám đốc Sản xuất của nhà máy gỗ, Mai tự tin mở màn hình và dùng Cursor trình chiếu trực tiếp (live-preview) một nguyên mẫu phần mềm (prototype) được sinh ra siêu nhanh bằng AI. Nhưng thay vì ấn tượng, vị Giám đốc lại tỏ ra giận dữ. Ông phàn nàn rằng giao diện này tuy hiện đại nhưng bắt công nhân phải bấm quá nhiều nút, phá vỡ thói quen làm việc 20 năm của họ. Không khí cuộc họp đóng băng. Đứng trước tình huống này, kỹ năng "độc bản" nào của Mai cần được kích hoạt ngay lập tức mà không một AI nào làm thay được?</v>
       </c>
       <c r="C7" t="str">
-        <v>single</v>
+        <v>multiple</v>
       </c>
       <c r="D7" t="str">
-        <v>["Thiếu hụt kỹ năng tiếng Anh và nền tảng lập trình cơ bản","Định kiến với công nghệ mới và sự ngại thay đổi quy trình chuẩn (Quán tính tư duy của chuyên gia)","Áp lực đồng lứa (Peer pressure) và nỗi sợ hãi AI sẽ cướp đi công việc","Không có ngân sách để mua các bản quyền phần mềm AI On-premise"]</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
+        <v>["Viết lại Prompt cho Cursor ngay tại chỗ để AI tự động vẽ lại giao diện ít nút hơn","Kỹ năng thấu cảm (Empathy): Lắng nghe nỗi sợ thay đổi của vị giám đốc để xoa dịu cảm xúc","Tư duy phản biện (Critical Thinking): Phân tích nhanh tại sao thói quen 20 năm lại quan trọng hơn giao diện đẹp","Kỹ năng phân tích dữ liệu (Data Literacy): Đưa ra số liệu chứng minh giao diện mới tiết kiệm thời gian hơn"]</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
       </c>
       <c r="F7" t="str">
-        <v/>
+        <v>[1,2]</v>
       </c>
       <c r="G7" t="str">
-        <v>Senior BA dễ vướng vào rào cản định kiến công nghệ và không muốn thay đổi quy trình đã quen thuộc (quán tính tư duy).</v>
+        <v>Khi xung đột xảy ra, EQ (Sự thấu cảm) và Tư duy phản biện để hiểu bản chất sự bảo thủ của người dùng là vũ khí duy nhất để gỡ rối chính trị dự án. Mọi cố gắng dùng AI lúc này đều vô tác dụng.</v>
       </c>
       <c r="H7" t="str">
-        <v>Senior BA,Rào cản</v>
+        <v>EQ,Thấu cảm</v>
       </c>
       <c r="I7">
         <v>3</v>
       </c>
       <c r="J7" t="str">
-        <v>Tư duy chuyển đổi</v>
+        <v>Trí tuệ cảm xúc</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Chuyển Trạng Thái</v>
+        <v>Chiếc Hộp Pandora</v>
       </c>
       <c r="B8" t="str">
-        <v>Một tập đoàn tài chính lớn tìm đến công ty Mai. Trách nhiệm BA được giao phó cho Mai. Thay vì cách làm cũ, Mai áp dụng quy trình "Intelligent Automation" ứng dụng AI. Hãy giúp Mai sắp xếp thứ tự hợp lý của các bước làm việc từ lúc nhận yêu cầu thô đến lúc ra giải pháp cuối cùng theo mô hình AI-Driven BA.</v>
+        <v>Một ngân hàng thuê công ty của Mai xây dựng mô hình AI tự động chấm điểm tín dụng (Credit Scoring). Ban Giám đốc ngân hàng ra chỉ thị: "Hãy thiết kế luồng quy trình để hệ thống duyệt vay mang lại lợi nhuận cao nhất bất chấp mọi yếu tố". Sau khi dùng AI chạy mô phỏng giả lập dữ liệu, Mai bàng hoàng phát hiện ra: Mô hình tự động đánh tụt điểm tín dụng và từ chối các khoản vay của phụ nữ mang thai (do rủi ro nghỉ thai sản giảm thu nhập). Hành động tiếp theo của Mai quyết định việc cô có phải là một "AI-Driven BA" mang tư duy làm chủ hay không. Hãy sắp xếp các bước xử lý thể hiện Trách nhiệm đạo đức cao nhất.</v>
       </c>
       <c r="C8" t="str">
         <v>ordering</v>
       </c>
       <c r="D8" t="str">
-        <v>["Thu thập các yêu cầu phi cấu trúc thô (Biên bản họp, ý tưởng rời rạc)","Cung cấp bối cảnh (Context) và yêu cầu thô cho AI kèm theo Prompt kỹ thuật","AI nhanh chóng sinh ra kịch bản nền tảng (Baseline) và tài liệu sơ khởi","Áp dụng 3 bộ lọc để thẩm định chất lượng và tính khả thi của kết quả AI","Tương tác trực quan và chốt phương án hoàn thiện với khách hàng"]</v>
+        <v>["Đình chỉ ngay luồng mô phỏng và lưu lại các bằng chứng phân biệt đối xử của mô hình","Áp dụng Bộ lọc Pháp lý &amp; Đạo đức (Ethics Filter) để đánh giá mức độ vi phạm luật bình đẳng","Tổng hợp báo cáo rủi ro thương hiệu và pháp lý nếu ngân hàng đưa mô hình này vào thực tế","Lên lịch họp khẩn với Ban Giám đốc ngân hàng để đối thoại và trình bày rủi ro","Đề xuất các ràng buộc (Constraints) và trọng số công bằng vào thuật toán để tái huấn luyện mô hình"]</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -644,266 +644,266 @@
         <v>[]</v>
       </c>
       <c r="G8" t="str">
-        <v>Sự dịch chuyển lớn của BA là dùng AI xử lý yêu cầu thô, sau đó thẩm định và nhanh chóng tương tác với khách hàng thay vì làm việc tuyến tính.</v>
+        <v>BA phải là người đứng ra chịu trách nhiệm giải trình (Accountability) và kiểm soát thiên kiến (Bias) của AI. Quy trình chuẩn: Dừng -&gt; Đánh giá -&gt; Báo cáo -&gt; Cảnh báo -&gt; Đề xuất sửa chữa.</v>
       </c>
       <c r="H8" t="str">
-        <v>Requirement,Chiến lược</v>
+        <v>Đạo đức,Rủi ro,Ethics</v>
       </c>
       <c r="I8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J8" t="str">
-        <v>Chiến lược phân tích</v>
+        <v>Tính trách nhiệm</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Món Quà Thời Gian</v>
+        <v>Vũ Điệu Của Dữ Liệu</v>
       </c>
       <c r="B9" t="str">
-        <v>Dự án A yêu cầu hoàn thành bộ tài liệu đặc tả (SRS) đồ sộ. Nhờ ứng dụng kỹ năng Prompt xuất sắc, Mai dùng AI và chỉ mất 1 ngày để hoàn thành thay vì 5 ngày ròng rã như trước đây (tiết kiệm 80% thời gian). Nhìn vào quỹ thời gian dư ra vô cùng lớn này, hướng đi nào sau đây là phù hợp nhất với vị thế của một "AI-Driven BA" thay vì một người thợ viết tài liệu?</v>
+        <v>Để trau dồi "Vũ khí mới" trong thời đại số, Mai đang học thêm kỹ năng Phân tích dữ liệu (Data Literacy). Cô có một file Excel chứa lịch sử 10,000 giao dịch thương mại điện tử bị hủy đơn. Thay vì tự tạo bảng Pivot, Mai muốn mượn sức AI (như Advanced Data Analysis của ChatGPT) để tìm ra "Insight" kinh doanh. Đâu là cách tiếp cận thể hiện tư duy của một BA thay vì một thợ gõ dữ liệu?</v>
       </c>
       <c r="C9" t="str">
-        <v>single</v>
+        <v>matching</v>
       </c>
       <c r="D9" t="str">
-        <v>["Dùng 4 ngày còn lại để nghỉ ngơi hoặc giải trí vì đã hoàn thành KPI","Chuyển hẳn sang làm Tester (QC) để bọc lót cho khâu kiểm thử","Dùng quỹ thời gian đó để tư duy hệ thống sâu hơn, làm việc chặt chẽ hơn với Stakeholder để đào sâu vấn đề và gia tăng tỷ lệ chốt giải pháp","Nhận thêm 4 dự án tương đương nữa để cày KPI số lượng tài liệu"]</v>
-      </c>
-      <c r="E9">
-        <v>2</v>
+        <v>["Hành động của thợ gõ (Thụ động)","Hành động của BA tập sự (Phụ thuộc)","Hành động của AI-Driven BA (Định hướng)","Hành động rủi ro (Vi phạm)"]</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
       </c>
       <c r="F9" t="str">
-        <v/>
+        <v>["\"Vẽ cho tôi biểu đồ tỷ lệ hủy đơn theo tháng.\"","\"File dữ liệu này nói về cái gì, hãy tìm ra lý do hủy đơn giúp tôi.\"","\"Dựa vào file dữ liệu, hãy tìm mối tương quan giữa thời gian giao hàng trễ và lý do hủy đơn, đồng thời đề xuất 3 quy trình logistics cần cải tiến.\"","Upload trực tiếp dữ liệu thô có chứa số điện thoại và email khách hàng lên Public AI"]</v>
       </c>
       <c r="G9" t="str">
-        <v>AI giải phóng thời gian làm việc chân tay để BA tập trung vào công việc tư duy chiến lược và tương tác khách hàng.</v>
+        <v>AI-Driven BA luôn gắn liền phân tích dữ liệu với mục tiêu cải tiến nghiệp vụ (Logistics) và tuyệt đối tuân thủ bảo mật.</v>
       </c>
       <c r="H9" t="str">
-        <v>Hiệu suất,Giá trị</v>
+        <v>Data Literacy,Insight</v>
       </c>
       <c r="I9">
         <v>1</v>
       </c>
       <c r="J9" t="str">
-        <v>Quản trị hiệu suất</v>
+        <v>Nâng cấp kỹ năng</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Bảo Chứng Niềm Tin</v>
+        <v>Đứng Trên Vai Người Khổng Lồ</v>
       </c>
       <c r="B10" t="str">
-        <v>Trong quá trình phân tích dữ liệu giao dịch của khách hàng (một ngân hàng) nhằm tối ưu quy trình thẩm định vay, Mai dự định sao chép 10,000 dòng dữ liệu hồ sơ thực tế chưa qua xử lý (Raw Data) đẩy lên một nền tảng Public AI để nhờ nó phát hiện quy luật. Xét theo góc độ đạo đức nghề nghiệp và các rào cản ứng dụng AI, hành động của Mai đã vi phạm nghiêm trọng vào bộ lọc kiểm định nào?</v>
+        <v>Mai được giao tiếp quản một hệ thống Node.js Legacy khổng lồ không có bất kỳ dòng tài liệu nào (Zero Documentation). Nhiệm vụ của cô là tìm ra các quy tắc tính chiết khấu (Discount Rules) đang ẩn sâu trong hàng trăm file code. Mai quyết định sử dụng Claude Code (hoặc Cursor) để rà quét. Tuy nhiên, hệ thống liên tục báo lỗi quá giới hạn ngữ cảnh (Context Window Limit) hoặc trả về kết quả ảo giác vì codebase quá lớn. Kỹ thuật phân tích nào sau đây thể hiện tư duy hệ thống (Systems Thinking) xuất sắc nhất của Mai để giải quyết triệt để bài toán này?</v>
       </c>
       <c r="C10" t="str">
         <v>single</v>
       </c>
       <c r="D10" t="str">
-        <v>["Bộ lọc Nghiệp vụ (Business Filter)","Bộ lọc Ngôn ngữ (Language Filter)","Bộ lọc Giá trị thực (Value Filter)","Bộ lọc Pháp lý &amp; Bảo mật (Privacy &amp; Security Filter) với nguy cơ rò rỉ dữ liệu tổ chức"]</v>
+        <v>["Bỏ cuộc với AI và tải toàn bộ code về máy đọc thủ công từng dòng một","Viết một câu lệnh yêu cầu AI phân tích toàn bộ cấu trúc thư mục và tự động đoán quy tắc","Áp dụng chiến lược Chia để trị (Divide &amp; Conquer): Yêu cầu AI vẽ Dependency Graph trước, khoanh vùng chính xác các file liên quan đến module thanh toán, rồi mới dùng AI phân tích sâu các file đó","Mua ngay bản trả phí đắt nhất của AI để tăng tối đa giới hạn Context Window"]</v>
       </c>
       <c r="E10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F10" t="str">
         <v/>
       </c>
       <c r="G10" t="str">
-        <v>Đẩy dữ liệu nhạy cảm lên Public AI vi phạm nghiêm trọng bộ lọc Pháp lý &amp; Bảo mật.</v>
+        <v>Tư duy hệ thống giúp BA biết cách chia nhỏ bài toán. Không một AI nào có thể tiêu hóa toàn bộ hệ thống lớn ngay lập tức. Chia để trị và phân tích theo Dependency là phương pháp thực chiến cao thủ.</v>
       </c>
       <c r="H10" t="str">
-        <v>Bảo mật,Rủi ro</v>
+        <v>Tư duy hệ thống,Claude Code</v>
       </c>
       <c r="I10">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J10" t="str">
-        <v>Bảo mật và Rủi ro</v>
+        <v>Tư duy hệ thống</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Trách Nhiệm Cuối Cùng</v>
+        <v>Bóng Đêm Ảo Giác</v>
       </c>
       <c r="B11" t="str">
-        <v>Dự án đang trong giai đoạn nước rút (Agile Sprint). Khách hàng liên tục thay đổi luồng nghiệp vụ kinh doanh. Để chạy đua tiến độ, Mai dùng AI sinh ra một thiết kế luồng quy trình (workflow) mới cực nhanh và chuyển thẳng cho đội Dev mà bỏ qua bước rà soát chéo. Khi Release, luồng này bị sai logic cơ bản khiến hệ thống thất thoát tiền. Giám đốc chất vấn: "Tại sao luồng này lại sai?". Mai biện minh: "Do AI nó viết ra như vậy". Dưới góc nhìn chuyên nghiệp của nghề BA trong kỷ nguyên số, câu trả lời này phản ánh sự thiếu hụt tố chất bất biến nào?</v>
+        <v>Hiện tượng AI Hallucination (Ảo giác AI) là bóng ma đáng sợ nhất đối với một BA. Trong lúc phân tích yêu cầu tích hợp cổng thanh toán trực tuyến, AI tự tin bịa ra một API endpoint giả mạo của PayPal và hướng dẫn Mai viết đặc tả kỹ thuật dựa trên API không tồn tại đó. Những kỹ năng cốt lõi nào của BA sẽ đóng vai trò là "chiếc khiên" bảo vệ hệ thống khỏi những đoạn tài liệu sai lệch này?</v>
       </c>
       <c r="C11" t="str">
-        <v>single</v>
+        <v>multiple</v>
       </c>
       <c r="D11" t="str">
-        <v>["Trí tuệ cảm xúc (Emotional Intelligence)","Sự nhạy bén về Nghiệp vụ &amp; Khả năng chịu trách nhiệm (Accountability) trước giải pháp","Tư duy thiết kế (Design Thinking)","Kiến thức chuyên sâu về Prompt Engineering"]</v>
-      </c>
-      <c r="E11">
-        <v>1</v>
+        <v>["Kỹ năng viết truy vấn SQL thành thạo để kiểm tra cơ sở dữ liệu","Tư duy Phản biện (Critical Thinking): Luôn đặt câu hỏi nghi ngờ và cross-check thông tin từ các nguồn tài liệu chính thống (Official API Docs)","Sự nhạy bén về Nghiệp vụ (Business Acumen): Nhận ra luồng dữ liệu do AI đề xuất không logic với chuẩn mực kế toán tài chính","Kỹ năng giao tiếp xuất sắc với khách hàng"]</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
       </c>
       <c r="F11" t="str">
-        <v/>
+        <v>[1,2]</v>
       </c>
       <c r="G11" t="str">
-        <v>AI không thể chịu trách nhiệm trước pháp luật hay công ty. BA phải là người kiểm soát và chịu trách nhiệm giải trình (Accountability) cuối cùng.</v>
+        <v>Tư duy phản biện (chứng thực nguồn gốc) và Sự nhạy bén nghiệp vụ (đánh giá tính logic) là hai tấm khiên chống lại ảo giác của AI.</v>
       </c>
       <c r="H11" t="str">
-        <v>Trách nhiệm,Đạo đức</v>
+        <v>Hallucination,Phản biện</v>
       </c>
       <c r="I11">
         <v>3</v>
       </c>
       <c r="J11" t="str">
-        <v>Tính trách nhiệm</v>
+        <v>Thẩm định giải pháp</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Bức Tranh Tổng Thể</v>
+        <v>Cạm Bẫy Đóng Gói</v>
       </c>
       <c r="B12" t="str">
-        <v>Hệ thống mà Mai phụ trách đòi hỏi tích hợp từ nhiều nền tảng kế toán cũ kỹ (Legacy systems) khác nhau, đan xen với bối cảnh văn hóa phòng ban phức tạp và những quy định ngầm của doanh nghiệp (Office Politics). Mai nhận ra rằng dù AI rất xuất sắc trong việc tìm câu trả lời từ dữ liệu cấu trúc, nó hoàn toàn bất lực trong việc giải bài toán này. Kỹ năng vô hình nào của Mai đang tỏa sáng mạnh mẽ nhất, khẳng định sự vượt trội của con người so với cỗ máy?</v>
+        <v>Khi sử dụng Agentic AI của Antigravity để hỗ trợ thiết kế cơ sở dữ liệu, Mai nhận được một bản vẽ sơ đồ thực thể liên kết (ERD) hoàn hảo về mặt học thuật (đạt chuẩn hóa 3NF). Mọi thứ đều được chia nhỏ thành các bảng rời rạc để tránh trùng lặp dữ liệu. Tuy nhiên, bằng kinh nghiệm thực chiến, Mai biết rằng hệ thống báo cáo (Reporting) của dự án này cần truy xuất hàng triệu bản ghi mỗi giây, nếu join hàng chục bảng 3NF sẽ làm sập server. Hãy sắp xếp các bước Mai cần làm để biến kết quả "sách giáo khoa" của AI thành một giải pháp "thực chiến".</v>
       </c>
       <c r="C12" t="str">
-        <v>single</v>
+        <v>ordering</v>
       </c>
       <c r="D12" t="str">
-        <v>["Kỹ năng thống kê dữ liệu Data Literacy","Khả năng thao tác với các phần mềm thiết kế UI","Tư duy hệ thống (Systems Thinking) và Khả năng giải quyết bài toán phức tạp (Complex Problem Solving)","Kỹ năng viết truy vấn dữ liệu SQL thuần thục"]</v>
-      </c>
-      <c r="E12">
-        <v>2</v>
+        <v>["Tiếp nhận bản thiết kế ERD chuẩn hóa (3NF) từ kết quả khởi tạo của AI","Phân tích yêu cầu phi chức năng (NFR): Nhận diện bài toán thắt cổ chai hiệu suất khi truy vấn báo cáo","Chủ động bẻ gãy quy tắc: Xác định các khu vực dữ liệu cần Phi chuẩn hóa (Denormalization)","Viết Prompt yêu cầu AI tái cấu trúc lại một phần ERD: Chấp nhận dư thừa dữ liệu để tối ưu tốc độ đọc","Chốt kiến trúc cơ sở dữ liệu thực chiến và trình bày lý do bảo vệ thiết kế trước đội Dev"]</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
       </c>
       <c r="F12" t="str">
-        <v/>
+        <v>[]</v>
       </c>
       <c r="G12" t="str">
-        <v>Tư duy hệ thống giúp kết nối các mảng kiến thức rời rạc, văn hóa và yếu tố con người - điều AI chưa thể liên kết linh hoạt.</v>
+        <v>BA cần vượt ra khỏi giới hạn lý thuyết để tối ưu cho môi trường thực tế (Performance NFR). Quá trình này đòi hỏi kiến thức kiến trúc phần mềm và bản lĩnh đưa ra quyết định.</v>
       </c>
       <c r="H12" t="str">
-        <v>Tư duy hệ thống,Bài toán phức tạp</v>
+        <v>NFR,Kiến trúc,Thực chiến</v>
       </c>
       <c r="I12">
         <v>4</v>
       </c>
       <c r="J12" t="str">
-        <v>Tư duy hệ thống</v>
+        <v>Chiến lược phân tích</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Căn Bệnh Sao Chép</v>
+        <v>Phép Cân Bằng</v>
       </c>
       <c r="B13" t="str">
-        <v>Vũ - một Fresher BA mới được nhận vào team của Mai - nổi tiếng với năng lực tạo ra những tập User Story dài hàng chục trang chỉ trong nháy mắt nhờ ChatGPT. Tuy nhiên, khi Tech Lead hỏi xoáy về logic phân quyền nghiệp vụ bên dưới các Story đó, Vũ lúng túng và không thể giải thích nổi. Mai nhận ra Vũ đang mắc phải "Bẫy của Junior" kinh điển khi sử dụng AI. Những biểu hiện cốt lõi nào minh chứng cho căn bệnh này? (Chọn nhiều đáp án)</v>
+        <v>Để sống sót và thăng tiến, Mai đang tự lập ra một Bản đồ Năng lực (Capability Map). Cô cần rạch ròi giữa những năng lực máy móc có thể tăng cường (Machine Augmented) và những tố chất vĩnh cửu thuộc về con người (Human Core). Hãy giúp Mai phân định các năng lực này.</v>
       </c>
       <c r="C13" t="str">
-        <v>multiple</v>
+        <v>matching</v>
       </c>
       <c r="D13" t="str">
-        <v>["Bị ngợp trước khối lượng từ ngữ bóng bẩy của AI, coi kết quả đó là chân lý và sao chép vô thức","Dành quá nhiều thời gian để thẩm định chéo kết quả sinh ra từ AI","Lười tư duy sâu, đánh mất cơ hội rèn luyện logic cấu trúc qua việc tự phân tích, tự sai và tự sửa","Có thói quen nghi ngờ và phản biện mọi kết quả mà AI cung cấp"]</v>
+        <v>["Tạo ra hàng loạt bộ test case bao phủ mọi rẽ nhánh nghiệp vụ","Xây dựng niềm tin và sự đồng thuận giữa nhiều phòng ban lợi ích đối lập","Khám phá \"Pain-point\" ngầm ẩn sau những yêu cầu vô lý của khách hàng","Tổng hợp tài liệu chuẩn mực SRS/BRD từ các nguồn thông tin rời rạc"]</v>
       </c>
       <c r="E13" t="str">
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>[0,2]</v>
+        <v>["Machine Augmented (Giao cho AI)","Human Core (Tố chất con người)","Human Core (Tố chất con người)","Machine Augmented (Giao cho AI)"]</v>
       </c>
       <c r="G13" t="str">
-        <v>BA Fresher thường thiếu kiến thức nền tảng để thẩm định AI, dễ lười tư duy sâu và lệ thuộc vào kết quả của máy.</v>
+        <v>Việc sinh testcase hay viết tài liệu là thế mạnh của AI. Việc thấu hiểu pain-point và đàm phán chính trị nội bộ là tố chất bất biến của con người.</v>
       </c>
       <c r="H13" t="str">
-        <v>Fresher,Sai lầm</v>
+        <v>Phân định,Vai trò</v>
       </c>
       <c r="I13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J13" t="str">
-        <v>Lỗi thường gặp của Fresher</v>
+        <v>Định hướng giải pháp</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Đường Lên Đỉnh</v>
+        <v>Giới Hạn Tối Thượng</v>
       </c>
       <c r="B14" t="str">
-        <v>Hành trình tiến hóa của một Business Analyst truyền thống để trở thành một "AI-Powered BA" xuất sắc đòi hỏi phải đi qua những nấc thang nhận thức. Hãy giúp Mai sắp xếp các cột mốc sau theo trình tự phát triển lý tưởng từ thấp đến cao.</v>
+        <v>Tại một tập đoàn công nghệ hàng đầu, có ý kiến đề xuất sa thải toàn bộ đội ngũ BA để thay thế bằng các Hệ thống AI Tự Hành (Autonomous Agents). Các hệ thống này được chứng minh là có thể đọc email khách hàng, tự tổng hợp yêu cầu, tự động vẽ quy trình và tự sinh code. Mọi người hoang mang tột độ. Tuy nhiên, Giám đốc Công nghệ (CTO) đã bác bỏ ý kiến này và khẳng định vai trò của Mai (một Senior AI-Driven BA) là "Giới hạn tối thượng không thể chạm tới". Lý do cốt lõi mang tính bản chất nào bảo vệ vị thế độc tôn của Mai?</v>
       </c>
       <c r="C14" t="str">
-        <v>ordering</v>
+        <v>single</v>
       </c>
       <c r="D14" t="str">
-        <v>["Nắm vững các kỹ năng lõi của BA (Tư duy hệ thống, phân tích nghiệp vụ, giao tiếp)","Bắt đầu sử dụng AI qua các tác vụ cơ bản (Sửa lỗi chính tả, dịch thuật)","Thành thạo kỹ năng Prompting chuyên sâu để sinh tài liệu khung (Baseline)","Sử dụng các bộ lọc chuyên gia để thẩm định và kiểm soát rủi ro từ AI","Tích hợp AI làm cốt lõi để đưa ra giải pháp kinh doanh thông minh (AI-Driven)"]</v>
-      </c>
-      <c r="E14" t="str">
-        <v/>
+        <v>["AI Tự hành yêu cầu chi phí vận hành (Token) quá lớn, đắt hơn trả lương cho con người","AI không có khả năng nhận thức rủi ro đạo đức, không có địa vị pháp lý để chịu trách nhiệm giải trình (Accountability) trước pháp luật và xã hội khi hệ thống sinh ra quyết định sai lầm","Khách hàng không biết cách gõ tiếng Anh để giao tiếp với AI Tự hành","AI Tự hành chưa thể sinh ra mã nguồn các ngôn ngữ lập trình cổ điển như COBOL"]</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
       </c>
       <c r="F14" t="str">
-        <v>[]</v>
+        <v/>
       </c>
       <c r="G14" t="str">
-        <v>Sự tiến hóa phải đi từ gốc rễ nghiệp vụ, dùng AI cơ bản, sau đó là brainstorm sâu, thẩm định chặt chẽ và vươn tới cấp độ giải pháp AI-Driven.</v>
+        <v>Tính chịu trách nhiệm (Accountability) là biên giới cuối cùng AI không thể vượt qua. Máy móc có thể tự hành, nhưng khi hệ thống gây tai nạn, chỉ có con người mới chịu trách nhiệm trước pháp luật.</v>
       </c>
       <c r="H14" t="str">
-        <v>Lộ trình,Tiến hóa</v>
+        <v>Bản chất,Tầm nhìn</v>
       </c>
       <c r="I14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J14" t="str">
-        <v>Triết lý nghề nghiệp</v>
+        <v>Tính trách nhiệm</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Khoảng Trống Giá Trị</v>
+        <v>Khoảng Trống Bất Biến</v>
       </c>
       <c r="B15" t="str">
-        <v>Một khách hàng Startup đặt bài toán: "Tôi muốn làm ứng dụng AI dự đoán tỷ số bóng đá". Thay vì cắm đầu viết ngay SRS, Mai quyết định áp dụng Tư duy thiết kế (Design Thinking) kết hợp sức mạnh của AI để tìm ra "nỗi đau" (pain-point) thực sự (chính là muốn giữ chân người dùng lâu hơn trên app). Hãy giúp Mai sắp xếp các bước tiếp cận đúng chuẩn của một BA chuyên nghiệp.</v>
+        <v>Trong các cuộc phỏng vấn tuyển dụng BA thế hệ mới, thay vì hỏi về cách vẽ UML, nhà tuyển dụng bắt đầu đưa ra các bài toán kinh doanh mở và yêu cầu ứng viên giải quyết cùng AI. Họ nhận ra rằng những BA xuất sắc nhất không phải là người viết Prompt dài nhất, mà là người biết hỏi đúng câu hỏi. Tố chất nào quyết định năng lực "hỏi đúng câu hỏi" (Ask the right questions) để khai phá sức mạnh AI?</v>
       </c>
       <c r="C15" t="str">
-        <v>ordering</v>
+        <v>multiple</v>
       </c>
       <c r="D15" t="str">
-        <v>["Đồng cảm (Empathize): Lắng nghe sâu và khám phá nỗi đau gốc rễ của khách hàng","Định nghĩa (Define): Tái định nghĩa lại bài toán từ dự đoán tỷ số sang tính năng Cộng đồng","Sáng tạo (Ideate): Dùng AI để Brainstorm và mở rộng vô số các ý tưởng mới lạ","Mô phỏng (Prototype): Mượn AI sinh nhanh một bản phác thảo giao diện/quy trình","Kiểm thử (Test): Đem bản phác thảo đi trình bày để lấy phản hồi ngay lập tức từ Stakeholders"]</v>
+        <v>["Khả năng nhớ thuộc lòng hàng ngàn mẫu Prompt có sẵn trên mạng","Tư duy hệ thống (Systems Thinking) để nhìn thấy cấu trúc của vấn đề","Sự hiểu biết sâu sắc về Ngữ cảnh nghiệp vụ (Domain Knowledge)","Tốc độ gõ phím và kỹ năng tiếng Anh tuyệt đỉnh"]</v>
       </c>
       <c r="E15" t="str">
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>[]</v>
+        <v>[1,2]</v>
       </c>
       <c r="G15" t="str">
-        <v>Quy trình Design Thinking kinh điển: Empathize -&gt; Define -&gt; Ideate (với AI) -&gt; Prototype (với AI) -&gt; Test.</v>
+        <v>Để đặt đúng câu hỏi, BA cần hiểu sâu nghiệp vụ (Domain Knowledge) và có khả năng xâu chuỗi vấn đề (Systems Thinking). Prompting chỉ là bề mặt.</v>
       </c>
       <c r="H15" t="str">
-        <v>Design Thinking,Giải pháp</v>
+        <v>Năng lực lõi,Tuyển dụng</v>
       </c>
       <c r="I15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J15" t="str">
-        <v>Định hướng giải pháp</v>
+        <v>Nâng cấp kỹ năng</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Đích Đến Tối Thượng</v>
+        <v>Khải Hoàn Ca</v>
       </c>
       <c r="B16" t="str">
-        <v>Hành trình vượt qua định kiến, trau dồi tri thức và áp dụng các bộ lọc giá trị đã giúp Mai chính thức trở thành một "AI-Driven BA" xuất sắc. Cô không còn cảm giác sợ hãi mà thực sự coi AI như một người đồng nghiệp đắc lực, nơi sự sắc lạnh của Trí tuệ Nhân tạo (AI) được hòa quyện hoàn hảo với sự ấm áp của Trí tuệ Cảm xúc (EQ) con người. Đứng trên đỉnh cao của sự thấu ngộ, Mai đã nhận ra một sự thật phũ phàng nhưng cũng đầy kiêu hãnh của nghề nghiệp. Theo tinh thần của Seminar, câu nói nào dưới đây đúc kết chính xác nhất chân lý sống còn của nghề BA trong kỷ nguyên số?</v>
+        <v>Vượt qua mọi định kiến, hoang mang và khủng hoảng, Mai đã thiết lập thành công mô hình làm việc "AI-Driven BA" cho toàn bộ chi nhánh. Tốc độ ra mắt sản phẩm tăng gấp 3, độ hài lòng khách hàng đạt đỉnh, và quan trọng nhất, Mai tìm lại được ngọn lửa đam mê với nghề. Nhìn lại chặng đường, Mai đúc kết một hành trình "Tiến hóa nhận thức" kinh điển mà bất kỳ BA nào cũng phải đi qua để sống sót trong kỷ nguyên số. Hãy sắp xếp hành trình tiến hóa vĩ đại đó.</v>
       </c>
       <c r="C16" t="str">
-        <v>single</v>
+        <v>ordering</v>
       </c>
       <c r="D16" t="str">
-        <v>["AI sẽ hoàn toàn thay thế và xóa sổ vai trò của Business Analyst trong vòng 5 năm tới","AI không thay thế bạn, nhưng một BA biết dùng AI và có tư duy AI sẽ thay thế bạn","Chỉ những BA có khả năng viết mã lập trình AI trực tiếp mới có thể tồn tại","Nghề BA thực ra sẽ không thay đổi gì cả, AI chỉ là một trào lưu nhất thời rồi sẽ qua đi"]</v>
-      </c>
-      <c r="E16">
-        <v>1</v>
+        <v>["Sợ hãi và Chối bỏ (Fear &amp; Denial): Cảm thấy bị đe dọa, tẩy chay AI và bám víu vào kinh nghiệm cũ","Ảo tưởng và Lệ thuộc (Illusion &amp; Dependency): Ngợp trước sức mạnh AI, dùng AI bừa bãi và nhắm mắt tin tưởng mọi kết quả","Khủng hoảng định hướng (Lost): Nhận ra AI sinh ra nhiều rác hơn là giá trị, hoang mang về con đường phát triển","Thức tỉnh và Làm chủ (Awakening &amp; Mastery): Tích hợp AI làm đòn bẩy, áp dụng các bộ lọc chuyên gia để kiểm soát hoàn toàn hệ thống","Tiến hóa hội tụ (Evolution): Trở thành nhà thiết kế giải pháp chiến lược, nơi EQ của con người hòa quyện cùng IQ của máy móc"]</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
       </c>
       <c r="F16" t="str">
-        <v/>
+        <v>[]</v>
       </c>
       <c r="G16" t="str">
-        <v>Chân lý: Công nghệ không thể tự động thay thế con người, nhưng con người làm chủ công nghệ sẽ chiến thắng.</v>
+        <v>Hành trình tiến hóa đi từ Sợ hãi -&gt; Ảo tưởng (lạm dụng) -&gt; Khủng hoảng -&gt; Làm chủ -&gt; Tiến hóa hoàn toàn. Đây là khải hoàn ca của một BA chân chính.</v>
       </c>
       <c r="H16" t="str">
-        <v>Tầm nhìn,Kết luận</v>
+        <v>Tiến hóa,Tầm nhìn</v>
       </c>
       <c r="I16">
         <v>4</v>
